--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0333906\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FAD4F0-842D-4A7A-82A6-AD3402C88F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8EF21F-BC49-41D8-AC93-AB2DCC20C97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>Onda 2</t>
-  </si>
-  <si>
-    <t>[resp]</t>
   </si>
   <si>
     <t>--</t>
@@ -589,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -673,6 +670,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -975,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -1007,7 +1005,7 @@
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
       <c r="D2" s="29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" s="23"/>
       <c r="F2" s="25" t="s">
@@ -1015,7 +1013,7 @@
       </c>
       <c r="G2" s="23"/>
       <c r="H2" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1064,22 +1062,22 @@
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1090,22 +1088,22 @@
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1116,22 +1114,22 @@
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1148,21 +1146,21 @@
         <v>15</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="19" t="s">
-        <v>107</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>13</v>
@@ -1174,21 +1172,21 @@
         <v>15</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>13</v>
@@ -1200,16 +1198,16 @@
         <v>15</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1226,16 +1224,16 @@
         <v>18</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1252,16 +1250,16 @@
         <v>18</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1272,22 +1270,22 @@
         <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1298,22 +1296,22 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1324,365 +1322,366 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>90</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>91</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G22" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>95</v>
-      </c>
       <c r="B24" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G24" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H24" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G25" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G26" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>101</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>102</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H27" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -1692,15 +1691,15 @@
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
     </row>
-    <row r="31" spans="1:8" ht="24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
@@ -1712,7 +1711,7 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
@@ -1724,7 +1723,7 @@
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" s="23"/>
       <c r="D34" s="23"/>
@@ -1735,7 +1734,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -1750,7 +1749,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -1764,7 +1763,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -1778,7 +1777,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -1806,6 +1805,7 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1820,80 +1820,80 @@
   <sheetData>
     <row r="1" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>55</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>57</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>63</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
